--- a/artfynd/A 11927-2022 artfynd.xlsx
+++ b/artfynd/A 11927-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11927-2022 artfynd.xlsx
+++ b/artfynd/A 11927-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74915998</v>
+        <v>74916143</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411117.3691801655</v>
+        <v>411272</v>
       </c>
       <c r="R2" t="n">
-        <v>6588216.478665977</v>
+        <v>6588194</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,27 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-07-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-07-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Grov björkhögstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74916144</v>
+        <v>74915998</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411275.0783252926</v>
+        <v>411117</v>
       </c>
       <c r="R3" t="n">
-        <v>6588200.551503915</v>
+        <v>6588216</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -909,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74915997</v>
+        <v>74916144</v>
       </c>
       <c r="B4" t="n">
-        <v>89794</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5321</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411096.2426309471</v>
+        <v>411275</v>
       </c>
       <c r="R4" t="n">
-        <v>6588055.600813433</v>
+        <v>6588201</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,27 +944,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-07-14</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-07-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Asplåga</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74916143</v>
+        <v>74915997</v>
       </c>
       <c r="B5" t="n">
-        <v>73680</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>306</v>
+        <v>5321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>411271.8648768618</v>
+        <v>411096</v>
       </c>
       <c r="R5" t="n">
-        <v>6588194.009235229</v>
+        <v>6588056</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,27 +1046,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-14</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Grov björkhögstubbe</t>
+          <t>Asplåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,6 +1080,200 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>74916149</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Karlstad I2-området, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>411368</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6588106</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Grava</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2018-07-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2018-07-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad, Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>74915996</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58815</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Karlstad I2-området, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>411218</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6587865</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grava</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2018-07-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2018-07-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad, Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11927-2022 artfynd.xlsx
+++ b/artfynd/A 11927-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74916143</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74915998</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74916144</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74915997</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74916149</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,8 +1304,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74915996</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>